--- a/Lab-trails/2026-02-19-pig-slurry.xlsx
+++ b/Lab-trails/2026-02-19-pig-slurry.xlsx
@@ -5,18 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-02-19-pig-slurry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFF52CCE-BA0B-4CA9-ABF2-542168997515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99EB9A80-010E-48FB-AE8C-FFD35FC3F0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Acidification" sheetId="1" r:id="rId1"/>
     <sheet name="TAN" sheetId="2" r:id="rId2"/>
     <sheet name="DM" sheetId="3" r:id="rId3"/>
+    <sheet name="TAN-app-rate" sheetId="4" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -121,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
   <si>
     <t>ID</t>
   </si>
@@ -268,6 +272,67 @@
   <si>
     <t>NAN</t>
   </si>
+  <si>
+    <t xml:space="preserve">ID </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">NH4-N [g/L] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stdev</t>
+    </r>
+  </si>
+  <si>
+    <t>NH4-N [kg/L]</t>
+  </si>
+  <si>
+    <t>NH4-N stdev [kg/L]</t>
+  </si>
+  <si>
+    <t>slurry target[g or mL]</t>
+  </si>
+  <si>
+    <t>slurry target [kg or L]</t>
+  </si>
+  <si>
+    <t>surface area [cm2]</t>
+  </si>
+  <si>
+    <t>surface area [ha]</t>
+  </si>
+  <si>
+    <t>Slurry app [L / ha]</t>
+  </si>
+  <si>
+    <t>NH4-N app mean [kg/ha]</t>
+  </si>
+  <si>
+    <t>NH4-N app stdev [kg/ha]</t>
+  </si>
+  <si>
+    <t>Ammonium carbonate std1</t>
+  </si>
+  <si>
+    <t>Ammonium carbonate std2</t>
+  </si>
+  <si>
+    <t>Pig slurry untreated</t>
+  </si>
+  <si>
+    <t>Pig slurry AA</t>
+  </si>
+  <si>
+    <t>Pig slurry SA</t>
+  </si>
 </sst>
 </file>
 
@@ -278,7 +343,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -290,6 +355,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -315,13 +386,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -337,6 +412,37 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="TAN"/>
+      <sheetName val="DM"/>
+      <sheetName val="pH"/>
+      <sheetName val="TAN-App-rate"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="13">
+          <cell r="G13">
+            <v>3.5846328082546735</v>
+          </cell>
+          <cell r="H13">
+            <v>0.18074382573656025</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1371,4 +1477,345 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60F406CE-4927-458F-88A4-52D1F2C0C195}">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="4">
+        <f>TAN!G10</f>
+        <v>3.4513943320656892</v>
+      </c>
+      <c r="C2" s="4">
+        <f>TAN!H10</f>
+        <v>0.12670438142092311</v>
+      </c>
+      <c r="D2" s="3">
+        <f>B2*10^-3</f>
+        <v>3.4513943320656892E-3</v>
+      </c>
+      <c r="E2">
+        <f>C2*10^-3</f>
+        <v>1.2670438142092311E-4</v>
+      </c>
+      <c r="F2" s="5">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <f>F2*10^-3</f>
+        <v>2E-3</v>
+      </c>
+      <c r="H2">
+        <v>28.27</v>
+      </c>
+      <c r="I2">
+        <f>H2*10^-8</f>
+        <v>2.8270000000000001E-7</v>
+      </c>
+      <c r="J2" s="7">
+        <f>G2/I2</f>
+        <v>7074.6374248319771</v>
+      </c>
+      <c r="K2" s="5">
+        <f>D2*J2</f>
+        <v>24.41736350948489</v>
+      </c>
+      <c r="L2" s="5">
+        <f>J2*E2</f>
+        <v>0.89638755869064812</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="4">
+        <f>TAN!G4</f>
+        <v>3.3898480646302196</v>
+      </c>
+      <c r="C3" s="4">
+        <f>TAN!H4</f>
+        <v>0.17307276808702957</v>
+      </c>
+      <c r="D3" s="3">
+        <f t="shared" ref="D3:E4" si="0">B3*10^-3</f>
+        <v>3.3898480646302196E-3</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="0"/>
+        <v>1.7307276808702958E-4</v>
+      </c>
+      <c r="F3" s="5">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G4" si="1">F3*10^-3</f>
+        <v>2E-3</v>
+      </c>
+      <c r="H3">
+        <v>28.27</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I4" si="2">H3*10^-8</f>
+        <v>2.8270000000000001E-7</v>
+      </c>
+      <c r="J3" s="7">
+        <f t="shared" ref="J3:J4" si="3">G3/I3</f>
+        <v>7074.6374248319771</v>
+      </c>
+      <c r="K3" s="5">
+        <f t="shared" ref="K3:K4" si="4">D3*J3</f>
+        <v>23.981945982527197</v>
+      </c>
+      <c r="L3" s="5">
+        <f t="shared" ref="L3:L4" si="5">J3*E3</f>
+        <v>1.224427082327765</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="4">
+        <f>TAN!G7</f>
+        <v>3.401054090893755</v>
+      </c>
+      <c r="C4" s="4">
+        <f>TAN!H7</f>
+        <v>9.2470994559334274E-2</v>
+      </c>
+      <c r="D4" s="3">
+        <f t="shared" si="0"/>
+        <v>3.4010540908937549E-3</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>9.2470994559334276E-5</v>
+      </c>
+      <c r="F4" s="5">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="1"/>
+        <v>2E-3</v>
+      </c>
+      <c r="H4">
+        <v>28.27</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="2"/>
+        <v>2.8270000000000001E-7</v>
+      </c>
+      <c r="J4" s="7">
+        <f t="shared" si="3"/>
+        <v>7074.6374248319771</v>
+      </c>
+      <c r="K4" s="5">
+        <f t="shared" si="4"/>
+        <v>24.061224555314855</v>
+      </c>
+      <c r="L4" s="5">
+        <f t="shared" si="5"/>
+        <v>0.65419875882090039</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="4">
+        <f>[1]TAN!G13</f>
+        <v>3.5846328082546735</v>
+      </c>
+      <c r="C5" s="4">
+        <f>[1]TAN!H13</f>
+        <v>0.18074382573656025</v>
+      </c>
+      <c r="D5" s="3">
+        <f>B5*10^-3</f>
+        <v>3.5846328082546736E-3</v>
+      </c>
+      <c r="E5">
+        <f>C5*10^-3</f>
+        <v>1.8074382573656026E-4</v>
+      </c>
+      <c r="F5" s="5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <f>F5*10^-3</f>
+        <v>2E-3</v>
+      </c>
+      <c r="H5">
+        <v>28.27</v>
+      </c>
+      <c r="I5">
+        <f>H5*10^-8</f>
+        <v>2.8270000000000001E-7</v>
+      </c>
+      <c r="J5" s="7">
+        <f>G5/I5</f>
+        <v>7074.6374248319771</v>
+      </c>
+      <c r="K5" s="5">
+        <f>D5*J5</f>
+        <v>25.359977419559062</v>
+      </c>
+      <c r="L5" s="5">
+        <f>J5*E5</f>
+        <v>1.2786970338631782</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="4">
+        <f>TAN!G10</f>
+        <v>3.4513943320656892</v>
+      </c>
+      <c r="C6" s="4">
+        <f>[1]TAN!H14</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <f t="shared" ref="D6:D7" si="6">B6*10^-3</f>
+        <v>3.4513943320656892E-3</v>
+      </c>
+      <c r="E6">
+        <f t="shared" ref="E6:E7" si="7">C6*10^-3</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <f t="shared" ref="G6:G7" si="8">F6*10^-3</f>
+        <v>2E-3</v>
+      </c>
+      <c r="H6">
+        <v>28.27</v>
+      </c>
+      <c r="I6">
+        <f t="shared" ref="I6:I7" si="9">H6*10^-8</f>
+        <v>2.8270000000000001E-7</v>
+      </c>
+      <c r="J6" s="7">
+        <f t="shared" ref="J6:J7" si="10">G6/I6</f>
+        <v>7074.6374248319771</v>
+      </c>
+      <c r="K6" s="5">
+        <f t="shared" ref="K6:K7" si="11">D6*J6</f>
+        <v>24.41736350948489</v>
+      </c>
+      <c r="L6" s="5">
+        <f t="shared" ref="L6:L7" si="12">J6*E6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="4">
+        <f>TAN!G12</f>
+        <v>3.5541601662597575</v>
+      </c>
+      <c r="C7" s="4">
+        <f>[1]TAN!H15</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <f t="shared" si="6"/>
+        <v>3.5541601662597575E-3</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="8"/>
+        <v>2E-3</v>
+      </c>
+      <c r="H7">
+        <v>28.27</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="9"/>
+        <v>2.8270000000000001E-7</v>
+      </c>
+      <c r="J7" s="7">
+        <f t="shared" si="10"/>
+        <v>7074.6374248319771</v>
+      </c>
+      <c r="K7" s="5">
+        <f t="shared" si="11"/>
+        <v>25.144394526068321</v>
+      </c>
+      <c r="L7" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>